--- a/data/raw/Subproceso-Proceso-Area.xlsx
+++ b/data/raw/Subproceso-Proceso-Area.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Documentos/Poli/Informe de desempeño Institucional 2025-1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Indicadores_Oportunidad_Mejora/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="354" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{091CAFCF-06F2-4B82-B996-6401CE54E695}"/>
+  <xr:revisionPtr revIDLastSave="375" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FB7B1D7-B0A2-45D3-ACC4-376420B18B67}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C8BB491-4D7A-4ED1-AB08-0ADDFA03A5A0}"/>
   </bookViews>
@@ -22,14 +22,14 @@
     <sheet name="Facultad" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$G$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$H$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Hoja1 (2)'!$A$1:$H$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Hoja2!$A$1:$D$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Rectoria!$A$1:$F$60</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId8"/>
+    <pivotCache cacheId="3" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="217">
   <si>
     <t>Área</t>
   </si>
@@ -708,7 +708,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -747,6 +747,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -840,7 +846,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -894,12 +900,23 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -978,7 +995,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Licec Ximena Silva Goyeneche" refreshedDate="45139.659256712963" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="59" xr:uid="{64466DA5-0995-4927-819D-C456FE77773E}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:F59" sheet="Hoja1"/>
+    <worksheetSource ref="A1:G59" sheet="Hoja1"/>
   </cacheSource>
   <cacheFields count="6">
     <cacheField name="Área" numFmtId="0">
@@ -1548,7 +1565,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -2134,18 +2151,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{494903EA-E058-4AE4-B481-B2575BC472D5}">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" customWidth="1"/>
-    <col min="6" max="6" width="40.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" customWidth="1"/>
+    <col min="7" max="7" width="40.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -2156,19 +2174,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -2178,18 +2199,21 @@
       <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="1"/>
+      <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -2199,18 +2223,21 @@
       <c r="C3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1"/>
+      <c r="G3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -2220,18 +2247,21 @@
       <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2"/>
+      <c r="G4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
@@ -2241,20 +2271,23 @@
       <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -2265,17 +2298,20 @@
         <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="1"/>
+      <c r="G6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>25</v>
       </c>
@@ -2285,18 +2321,21 @@
       <c r="C7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="5"/>
+      <c r="G7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,18 +2345,21 @@
       <c r="C8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>33</v>
       </c>
@@ -2327,18 +2369,21 @@
       <c r="C9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>37</v>
       </c>
@@ -2349,17 +2394,20 @@
         <v>39</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="6"/>
+      <c r="G10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>42</v>
       </c>
@@ -2369,18 +2417,21 @@
       <c r="C11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="6"/>
+      <c r="G11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>42</v>
       </c>
@@ -2391,17 +2442,20 @@
         <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="6"/>
+      <c r="G12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>37</v>
       </c>
@@ -2412,17 +2466,20 @@
         <v>39</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="1"/>
+      <c r="G13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>48</v>
       </c>
@@ -2432,18 +2489,21 @@
       <c r="C14" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="2"/>
+      <c r="G14" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>52</v>
       </c>
@@ -2453,18 +2513,21 @@
       <c r="C15" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="5"/>
+      <c r="G15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>56</v>
       </c>
@@ -2474,18 +2537,21 @@
       <c r="C16" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="1"/>
+      <c r="G16" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
@@ -2496,17 +2562,20 @@
         <v>31</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="1"/>
+      <c r="G17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>60</v>
       </c>
@@ -2517,17 +2586,20 @@
         <v>60</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="1"/>
+      <c r="G18" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>48</v>
       </c>
@@ -2537,18 +2609,21 @@
       <c r="C19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="2"/>
+      <c r="G19" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>64</v>
       </c>
@@ -2558,18 +2633,21 @@
       <c r="C20" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="1"/>
+      <c r="G20" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>67</v>
       </c>
@@ -2579,18 +2657,21 @@
       <c r="C21" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="6"/>
+      <c r="G21" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>60</v>
       </c>
@@ -2600,18 +2681,21 @@
       <c r="C22" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="1"/>
+      <c r="G22" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>60</v>
       </c>
@@ -2622,17 +2706,20 @@
         <v>60</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="1"/>
+      <c r="G23" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>48</v>
       </c>
@@ -2642,18 +2729,21 @@
       <c r="C24" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="2"/>
+      <c r="G24" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>74</v>
       </c>
@@ -2663,18 +2753,21 @@
       <c r="C25" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="7"/>
+      <c r="G25" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>37</v>
       </c>
@@ -2685,17 +2778,20 @@
         <v>39</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="6"/>
+      <c r="G26" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>79</v>
       </c>
@@ -2706,17 +2802,20 @@
         <v>81</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="6"/>
+      <c r="G27" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>83</v>
       </c>
@@ -2726,18 +2825,21 @@
       <c r="C28" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="6"/>
+      <c r="G28" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>86</v>
       </c>
@@ -2747,18 +2849,21 @@
       <c r="C29" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="1"/>
+      <c r="G29" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="H29" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>90</v>
       </c>
@@ -2769,17 +2874,20 @@
         <v>92</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="6"/>
+      <c r="G30" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>94</v>
       </c>
@@ -2789,18 +2897,21 @@
       <c r="C31" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="1"/>
+      <c r="G31" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="H31" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>97</v>
       </c>
@@ -2810,18 +2921,21 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="5"/>
+      <c r="G32" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="H32" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>90</v>
       </c>
@@ -2832,17 +2946,20 @@
         <v>92</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="6"/>
+      <c r="G33" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="H33" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>79</v>
       </c>
@@ -2853,17 +2970,20 @@
         <v>69</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="6"/>
+      <c r="G34" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="H34" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>37</v>
       </c>
@@ -2874,17 +2994,20 @@
         <v>103</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="6"/>
+      <c r="G35" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="H35" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>79</v>
       </c>
@@ -2895,17 +3018,20 @@
         <v>81</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="1"/>
+      <c r="G36" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="H36" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>105</v>
       </c>
@@ -2915,18 +3041,21 @@
       <c r="C37" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="5"/>
+      <c r="G37" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>108</v>
       </c>
@@ -2936,20 +3065,23 @@
       <c r="C38" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="F38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="H38" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>52</v>
       </c>
@@ -2959,18 +3091,21 @@
       <c r="C39" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="5"/>
+      <c r="G39" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="H39" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>37</v>
       </c>
@@ -2981,17 +3116,20 @@
         <v>103</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E40" s="6"/>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="6"/>
+      <c r="G40" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>90</v>
       </c>
@@ -3002,17 +3140,20 @@
         <v>103</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E41" s="6"/>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="6"/>
+      <c r="G41" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="H41" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>114</v>
       </c>
@@ -3022,18 +3163,21 @@
       <c r="C42" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="1"/>
+      <c r="G42" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>114</v>
       </c>
@@ -3044,17 +3188,20 @@
         <v>88</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="1"/>
+      <c r="G43" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="H43" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>119</v>
       </c>
@@ -3064,18 +3211,21 @@
       <c r="C44" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="5"/>
+      <c r="G44" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="H44" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>37</v>
       </c>
@@ -3086,17 +3236,20 @@
         <v>125</v>
       </c>
       <c r="D45" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="1"/>
+      <c r="G45" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="H45" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>10</v>
       </c>
@@ -3106,18 +3259,21 @@
       <c r="C46" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="5"/>
+      <c r="G46" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>37</v>
       </c>
@@ -3128,17 +3284,20 @@
         <v>103</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="1"/>
+      <c r="G47" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="H47" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>37</v>
       </c>
@@ -3149,17 +3308,20 @@
         <v>39</v>
       </c>
       <c r="D48" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="1"/>
+      <c r="G48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>129</v>
       </c>
@@ -3169,18 +3331,21 @@
       <c r="C49" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="E49" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="5"/>
+      <c r="G49" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="H49" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="13" t="s">
         <v>129</v>
       </c>
@@ -3190,37 +3355,43 @@
       <c r="C50" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E50" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1" t="s">
+      <c r="F50" s="5"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="23" t="s">
         <v>134</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="4" t="s">
+      <c r="F51" s="5"/>
+      <c r="G51" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="H51" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>132</v>
       </c>
@@ -3230,16 +3401,19 @@
       <c r="C52" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E52" s="4"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="4" t="s">
+      <c r="F52" s="4"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>132</v>
       </c>
@@ -3249,16 +3423,19 @@
       <c r="C53" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E53" s="4"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="4" t="s">
+      <c r="F53" s="4"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>132</v>
       </c>
@@ -3268,16 +3445,19 @@
       <c r="C54" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E54" s="4"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="4" t="s">
+      <c r="F54" s="4"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>135</v>
       </c>
@@ -3287,18 +3467,21 @@
       <c r="C55" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="1"/>
+      <c r="G55" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="H55" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
         <v>137</v>
       </c>
@@ -3308,16 +3491,19 @@
       <c r="C56" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E56" s="1"/>
       <c r="F56" s="1"/>
-      <c r="G56" s="4" t="s">
+      <c r="G56" s="1"/>
+      <c r="H56" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>138</v>
       </c>
@@ -3327,16 +3513,19 @@
       <c r="C57" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E57" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="4" t="s">
+      <c r="G57" s="1"/>
+      <c r="H57" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
         <v>139</v>
       </c>
@@ -3346,16 +3535,19 @@
       <c r="C58" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-      <c r="G58" s="1" t="s">
+      <c r="G58" s="1"/>
+      <c r="H58" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="14" t="s">
         <v>140</v>
       </c>
@@ -3365,16 +3557,19 @@
       <c r="C59" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="4" t="s">
+      <c r="G59" s="1"/>
+      <c r="H59" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="14" t="s">
         <v>140</v>
       </c>
@@ -3384,16 +3579,19 @@
       <c r="C60" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E60" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="1" t="s">
+      <c r="G60" s="1"/>
+      <c r="H60" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>143</v>
       </c>
@@ -3404,15 +3602,18 @@
         <v>146</v>
       </c>
       <c r="D61" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="4" t="s">
+      <c r="G61" s="1"/>
+      <c r="H61" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="14" t="s">
         <v>174</v>
       </c>
@@ -3422,21 +3623,28 @@
       <c r="C62" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1" t="s">
+      <c r="G62" s="1"/>
+      <c r="H62" s="1" t="s">
         <v>151</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H62" xr:uid="{494903EA-E058-4AE4-B481-B2575BC472D5}"/>
+  <conditionalFormatting sqref="D2:D55">
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B55">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7453,15 +7661,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -7696,6 +7895,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
   <ds:schemaRefs>
@@ -7708,14 +7916,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12D41D8-D34A-4C1F-82E4-8461693B79B3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7732,4 +7932,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/Subproceso-Proceso-Area.xlsx
+++ b/data/raw/Subproceso-Proceso-Area.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Indicadores_Oportunidad_Mejora/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="375" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FB7B1D7-B0A2-45D3-ACC4-376420B18B67}"/>
+  <xr:revisionPtr revIDLastSave="406" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DC87CFE-5269-4D43-8FC3-804486E1EB87}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C8BB491-4D7A-4ED1-AB08-0ADDFA03A5A0}"/>
   </bookViews>
@@ -22,14 +22,14 @@
     <sheet name="Facultad" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$H$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$G$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Hoja1 (2)'!$A$1:$H$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Hoja2!$A$1:$D$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Rectoria!$A$1:$F$60</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId8"/>
+    <pivotCache cacheId="8" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="219">
   <si>
     <t>Área</t>
   </si>
@@ -702,6 +702,12 @@
   </si>
   <si>
     <t>Operaciones Académicas</t>
+  </si>
+  <si>
+    <t>SECRETARIA ACADÉMICA Y DE DOCENCIA</t>
+  </si>
+  <si>
+    <t>Vicerrectoría financiera y administrativa</t>
   </si>
 </sst>
 </file>
@@ -751,8 +757,10 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color indexed="8"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -846,7 +854,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -900,23 +908,26 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -995,7 +1006,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Licec Ximena Silva Goyeneche" refreshedDate="45139.659256712963" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="59" xr:uid="{64466DA5-0995-4927-819D-C456FE77773E}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:G59" sheet="Hoja1"/>
+    <worksheetSource ref="A1:F59" sheet="Hoja1"/>
   </cacheSource>
   <cacheFields count="6">
     <cacheField name="Área" numFmtId="0">
@@ -1565,7 +1576,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -2151,143 +2162,127 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{494903EA-E058-4AE4-B481-B2575BC472D5}">
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
-    <col min="7" max="7" width="40.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" customWidth="1"/>
+    <col min="6" max="6" width="40.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="8" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="4" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="2"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="G4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="E5" s="27" t="s">
         <v>22</v>
       </c>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="G5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -2298,765 +2293,669 @@
         <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="4" t="s">
+      <c r="E6" s="1"/>
+      <c r="F6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5"/>
+      <c r="D7" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="G7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="G8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="G9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="24" t="s">
         <v>37</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>39</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="6"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="G10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="F11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="1" t="s">
+      <c r="E12" s="24"/>
+      <c r="F12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="G13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H13" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="23" t="s">
         <v>48</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="2"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="G14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H14" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="5"/>
+      <c r="D15" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="G15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H15" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="G16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H16" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="D17" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="G17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1" t="s">
+        <v>215</v>
+      </c>
       <c r="G18" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H18" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="23" t="s">
         <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F19" s="2"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="G19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H19" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="G20" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H20" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F21" s="6"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="G21" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H21" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="G22" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H22" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1" t="s">
+        <v>214</v>
+      </c>
       <c r="G23" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="H23" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="23" t="s">
         <v>48</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E24" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F24" s="2"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="G24" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H24" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F25" s="7"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="G25" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H25" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="24" t="s">
         <v>37</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="D26" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="6"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="G26" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H26" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="24" t="s">
         <v>79</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="6"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="G27" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H27" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F28" s="6"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="G28" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H28" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1" t="s">
+        <v>89</v>
+      </c>
       <c r="G29" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H29" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
+    <row r="30" spans="1:7" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="24" t="s">
         <v>90</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="D30" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E30" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F30" s="6"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="G30" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H30" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E31" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="G31" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H31" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="5"/>
+      <c r="D32" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E32" s="13"/>
+      <c r="F32" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="G32" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H32" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:7" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="24" t="s">
         <v>90</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>92</v>
-      </c>
       <c r="D33" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E33" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F33" s="6"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="G33" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H33" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="24" t="s">
         <v>79</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="D34" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F34" s="6"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="G34" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H34" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
-        <v>37</v>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="24" t="s">
+        <v>217</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="D35" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E35" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F35" s="6"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="G35" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H35" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>81</v>
-      </c>
       <c r="D36" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="G36" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H36" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="5" t="s">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="5"/>
+      <c r="D37" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="1" t="s">
+        <v>107</v>
+      </c>
       <c r="G37" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="H37" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="23" t="s">
         <v>108</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -3065,586 +2964,507 @@
       <c r="C38" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E38" s="4" t="s">
+      <c r="D38" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="E38" s="23" t="s">
         <v>22</v>
       </c>
+      <c r="F38" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="G38" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H38" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="13" t="s">
         <v>52</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="D39" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="5"/>
+        <v>218</v>
+      </c>
+      <c r="E39" s="13"/>
+      <c r="F39" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="G39" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H39" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
-        <v>37</v>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="24" t="s">
+        <v>217</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="D40" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" s="24"/>
+      <c r="F40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F40" s="6"/>
-      <c r="G40" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H40" s="1" t="s">
+      <c r="C41" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="24"/>
+      <c r="F41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F41" s="6"/>
-      <c r="G41" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="E42" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="G42" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="H42" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>114</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="D43" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E43" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="G43" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="H43" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="E44" s="4" t="s">
+      <c r="D44" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="F44" s="5"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="1" t="s">
+        <v>123</v>
+      </c>
       <c r="G44" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H44" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D45" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H45" s="1" t="s">
+      <c r="C46" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" s="13"/>
+      <c r="F46" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="5"/>
-      <c r="G46" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="D47" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E47" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="G47" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H47" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="D48" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E48" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="G48" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H48" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="E49" s="4" t="s">
+      <c r="D49" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="F49" s="5"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="G49" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H49" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="13" t="s">
         <v>129</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E50" s="4" t="s">
+      <c r="D50" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="F50" s="5"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1" t="s">
+      <c r="E50" s="13"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="s">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D51" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="E51" s="4" t="s">
+      <c r="D51" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F51" s="5"/>
-      <c r="G51" s="4" t="s">
+      <c r="E51" s="13"/>
+      <c r="F51" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="G51" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="D52" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="4"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="D53" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" s="4"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F53" s="4"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="D54" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" s="4"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F54" s="4"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>135</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E55" s="4" t="s">
+      <c r="D55" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="G55" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="H55" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="12" t="s">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D56" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="E56" s="4" t="s">
+      <c r="D56" s="4" t="s">
         <v>76</v>
       </c>
+      <c r="E56" s="1"/>
       <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="4" t="s">
+      <c r="G56" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="14" t="s">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D57" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="E57" s="4" t="s">
+      <c r="D57" s="4" t="s">
         <v>76</v>
       </c>
+      <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="4" t="s">
+      <c r="G57" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="12" t="s">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C58" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="E58" s="4" t="s">
+      <c r="D58" s="4" t="s">
         <v>76</v>
       </c>
+      <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1" t="s">
+      <c r="G58" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="14" t="s">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="D59" s="14" t="s">
+      <c r="D59" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="E59" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="B60" s="14" t="s">
+      <c r="B60" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C60" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="C60" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D60" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="E60" s="4" t="s">
+      <c r="D60" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1" t="s">
+      <c r="G60" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>143</v>
       </c>
       <c r="B61" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>146</v>
-      </c>
+      <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="4" t="s">
+      <c r="G61" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="14" t="s">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="B62" s="19" t="s">
+      <c r="B62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D62" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="E62" s="4" t="s">
+      <c r="D62" s="4" t="s">
         <v>76</v>
       </c>
+      <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1" t="s">
+      <c r="G62" s="1" t="s">
         <v>151</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H62" xr:uid="{494903EA-E058-4AE4-B481-B2575BC472D5}"/>
-  <conditionalFormatting sqref="D2:D55">
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3">
+  <conditionalFormatting sqref="B3">
     <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B55">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="C2:C55">
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5135,10 +4955,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B56">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5920,7 +5740,7 @@
     </filterColumn>
   </autoFilter>
   <conditionalFormatting sqref="B2:B52">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6996,7 +6816,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B53">
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7650,14 +7470,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7896,21 +7714,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7935,9 +7752,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/raw/Subproceso-Proceso-Area.xlsx
+++ b/data/raw/Subproceso-Proceso-Area.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="406" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DC87CFE-5269-4D43-8FC3-804486E1EB87}"/>
+  <xr:revisionPtr revIDLastSave="408" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC0E2DAE-4DB9-4FF9-AB0D-5789641E9BAC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C8BB491-4D7A-4ED1-AB08-0ADDFA03A5A0}"/>
   </bookViews>
@@ -29,7 +29,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1576,7 +1576,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -7470,12 +7470,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7714,20 +7716,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7752,12 +7755,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/raw/Subproceso-Proceso-Area.xlsx
+++ b/data/raw/Subproceso-Proceso-Area.xlsx
@@ -1,35 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="408" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC0E2DAE-4DB9-4FF9-AB0D-5789641E9BAC}"/>
+  <xr:revisionPtr revIDLastSave="421" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD0FC282-F7D4-4E70-8154-F2AF5A617FA6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C8BB491-4D7A-4ED1-AB08-0ADDFA03A5A0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja1 (2)" sheetId="7" r:id="rId2"/>
-    <sheet name="Hoja2" sheetId="8" r:id="rId3"/>
-    <sheet name="Rectoria" sheetId="4" r:id="rId4"/>
-    <sheet name="Hoja3" sheetId="3" r:id="rId5"/>
-    <sheet name="Facultades" sheetId="5" r:id="rId6"/>
-    <sheet name="Facultad" sheetId="6" r:id="rId7"/>
+    <sheet name="Proceso" sheetId="9" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
+    <sheet name="Hoja1 (2)" sheetId="7" r:id="rId3"/>
+    <sheet name="Hoja2" sheetId="8" r:id="rId4"/>
+    <sheet name="Rectoria" sheetId="4" r:id="rId5"/>
+    <sheet name="Hoja3" sheetId="3" r:id="rId6"/>
+    <sheet name="Facultades" sheetId="5" r:id="rId7"/>
+    <sheet name="Facultad" sheetId="6" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$G$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Hoja1 (2)'!$A$1:$H$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Hoja2!$A$1:$D$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Rectoria!$A$1:$F$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja1!$A$1:$G$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hoja1 (2)'!$A$1:$H$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Hoja2!$A$1:$D$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proceso!$B$1:$D$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Rectoria!$A$1:$F$60</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -51,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="219">
   <si>
     <t>Área</t>
   </si>
@@ -927,7 +929,27 @@
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2161,6 +2183,770 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{556B4589-4764-4BC7-BA72-702E47300540}">
+  <dimension ref="A1:D53"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="40.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B3">
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C51">
+    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{494903EA-E058-4AE4-B481-B2575BC472D5}">
   <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3470,7 +4256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76A3815-5892-4C99-B745-3DE1E81454E6}">
   <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4964,7 +5750,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{154EAF1E-6883-4B0B-A2D9-067B363C2FFC}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D54"/>
@@ -5746,7 +6532,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF49452F-6694-4E84-89FB-9A589F7853A9}">
   <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6822,7 +7608,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{415937D2-4A11-42B5-9451-DABCF2D474AD}">
   <dimension ref="A3:B44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7148,7 +7934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D7EB416-80A1-413A-B0A9-90751F171142}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7386,7 +8172,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED77C594-5CA7-4D8F-AD2C-ACEFB7BC74FD}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7470,17 +8256,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -7715,6 +8490,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -7725,17 +8511,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12D41D8-D34A-4C1F-82E4-8461693B79B3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7754,6 +8529,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
   <ds:schemaRefs>

--- a/data/raw/Subproceso-Proceso-Area.xlsx
+++ b/data/raw/Subproceso-Proceso-Area.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="427" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{111378DA-9568-48F8-A326-072E06712C53}"/>
+  <xr:revisionPtr revIDLastSave="429" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65C0B6F2-2F98-42D4-974D-DC3E00A00456}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C8BB491-4D7A-4ED1-AB08-0ADDFA03A5A0}"/>
   </bookViews>
@@ -31,7 +31,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId9"/>
+    <pivotCache cacheId="3" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1023,6 +1023,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1598,7 +1602,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -2184,6 +2188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{556B4589-4764-4BC7-BA72-702E47300540}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2207,7 +2212,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>218</v>
       </c>
@@ -2221,7 +2226,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -2235,7 +2240,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -2249,7 +2254,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>213</v>
       </c>
@@ -2263,7 +2268,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -2277,7 +2282,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>218</v>
       </c>
@@ -2291,7 +2296,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>213</v>
       </c>
@@ -2305,7 +2310,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>35</v>
       </c>
@@ -2319,7 +2324,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>35</v>
       </c>
@@ -2333,7 +2338,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
@@ -2347,7 +2352,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
@@ -2375,7 +2380,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
@@ -2389,7 +2394,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>218</v>
       </c>
@@ -2403,7 +2408,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>213</v>
       </c>
@@ -2417,7 +2422,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>213</v>
       </c>
@@ -2431,7 +2436,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>213</v>
       </c>
@@ -2445,7 +2450,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
@@ -2459,7 +2464,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>16</v>
       </c>
@@ -2473,7 +2478,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>35</v>
       </c>
@@ -2487,7 +2492,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>213</v>
       </c>
@@ -2501,7 +2506,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>213</v>
       </c>
@@ -2515,7 +2520,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>16</v>
       </c>
@@ -2529,7 +2534,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>76</v>
       </c>
@@ -2557,7 +2562,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
@@ -2571,7 +2576,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>16</v>
       </c>
@@ -2585,7 +2590,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
@@ -2599,7 +2604,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>16</v>
       </c>
@@ -2613,7 +2618,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>213</v>
       </c>
@@ -2627,7 +2632,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>218</v>
       </c>
@@ -2641,7 +2646,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>16</v>
       </c>
@@ -2655,7 +2660,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
@@ -2669,7 +2674,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>35</v>
       </c>
@@ -2683,7 +2688,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
@@ -2697,7 +2702,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>218</v>
       </c>
@@ -2711,7 +2716,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>16</v>
       </c>
@@ -2725,7 +2730,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>218</v>
       </c>
@@ -2739,7 +2744,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>35</v>
       </c>
@@ -2753,7 +2758,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>16</v>
       </c>
@@ -2767,7 +2772,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>16</v>
       </c>
@@ -2781,7 +2786,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>16</v>
       </c>
@@ -2795,7 +2800,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>122</v>
       </c>
@@ -2809,7 +2814,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>35</v>
       </c>
@@ -2823,7 +2828,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>12</v>
       </c>
@@ -2837,7 +2842,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>35</v>
       </c>
@@ -2851,7 +2856,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>35</v>
       </c>
@@ -2865,7 +2870,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>122</v>
       </c>
@@ -2879,7 +2884,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>122</v>
       </c>
@@ -2893,7 +2898,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>12</v>
       </c>
@@ -2907,7 +2912,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>35</v>
       </c>
@@ -2921,7 +2926,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>76</v>
       </c>
@@ -2936,6 +2941,14 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D53" xr:uid="{556B4589-4764-4BC7-BA72-702E47300540}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Centro de Medios Audiovisuales"/>
+        <filter val="Editorial y Publicaciones"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="B3">
     <cfRule type="duplicateValues" dxfId="7" priority="1"/>
   </conditionalFormatting>
@@ -8257,6 +8270,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -8491,27 +8524,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12D41D8-D34A-4C1F-82E4-8461693B79B3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8528,23 +8560,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/Subproceso-Proceso-Area.xlsx
+++ b/data/raw/Subproceso-Proceso-Area.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="429" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65C0B6F2-2F98-42D4-974D-DC3E00A00456}"/>
+  <xr:revisionPtr revIDLastSave="431" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D669B864-85E7-4E6B-AE1B-A9BCF0892C35}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C8BB491-4D7A-4ED1-AB08-0ADDFA03A5A0}"/>
   </bookViews>
@@ -31,7 +31,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1602,7 +1602,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -2188,7 +2188,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{556B4589-4764-4BC7-BA72-702E47300540}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2212,7 +2211,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>218</v>
       </c>
@@ -2226,7 +2225,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -2240,7 +2239,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -2254,7 +2253,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>213</v>
       </c>
@@ -2268,7 +2267,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -2282,7 +2281,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>218</v>
       </c>
@@ -2296,7 +2295,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>213</v>
       </c>
@@ -2310,7 +2309,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>35</v>
       </c>
@@ -2324,7 +2323,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>35</v>
       </c>
@@ -2338,7 +2337,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
@@ -2352,7 +2351,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
@@ -2380,7 +2379,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
@@ -2394,7 +2393,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>218</v>
       </c>
@@ -2408,7 +2407,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>213</v>
       </c>
@@ -2422,7 +2421,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>213</v>
       </c>
@@ -2436,7 +2435,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>213</v>
       </c>
@@ -2450,7 +2449,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
@@ -2464,7 +2463,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>16</v>
       </c>
@@ -2478,7 +2477,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>35</v>
       </c>
@@ -2492,7 +2491,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>213</v>
       </c>
@@ -2506,7 +2505,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>213</v>
       </c>
@@ -2520,7 +2519,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>16</v>
       </c>
@@ -2534,7 +2533,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>76</v>
       </c>
@@ -2562,7 +2561,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
@@ -2576,7 +2575,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>16</v>
       </c>
@@ -2590,7 +2589,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
@@ -2604,7 +2603,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>16</v>
       </c>
@@ -2618,7 +2617,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>213</v>
       </c>
@@ -2632,7 +2631,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>218</v>
       </c>
@@ -2646,7 +2645,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>16</v>
       </c>
@@ -2660,7 +2659,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
@@ -2674,7 +2673,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>35</v>
       </c>
@@ -2688,7 +2687,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
@@ -2702,7 +2701,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>218</v>
       </c>
@@ -2716,7 +2715,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>16</v>
       </c>
@@ -2730,7 +2729,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>218</v>
       </c>
@@ -2744,7 +2743,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>35</v>
       </c>
@@ -2758,7 +2757,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>16</v>
       </c>
@@ -2772,7 +2771,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>16</v>
       </c>
@@ -2786,7 +2785,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>16</v>
       </c>
@@ -2800,7 +2799,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>122</v>
       </c>
@@ -2814,7 +2813,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>35</v>
       </c>
@@ -2828,7 +2827,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>12</v>
       </c>
@@ -2842,7 +2841,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>35</v>
       </c>
@@ -2856,7 +2855,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>35</v>
       </c>
@@ -2870,7 +2869,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>122</v>
       </c>
@@ -2884,7 +2883,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>122</v>
       </c>
@@ -2898,7 +2897,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>12</v>
       </c>
@@ -2912,7 +2911,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>35</v>
       </c>
@@ -2926,7 +2925,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>76</v>
       </c>
@@ -2941,14 +2940,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D53" xr:uid="{556B4589-4764-4BC7-BA72-702E47300540}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Centro de Medios Audiovisuales"/>
-        <filter val="Editorial y Publicaciones"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D53" xr:uid="{556B4589-4764-4BC7-BA72-702E47300540}"/>
   <conditionalFormatting sqref="B3">
     <cfRule type="duplicateValues" dxfId="7" priority="1"/>
   </conditionalFormatting>
@@ -8270,26 +8262,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -8524,10 +8496,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12D41D8-D34A-4C1F-82E4-8461693B79B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8544,20 +8547,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12D41D8-D34A-4C1F-82E4-8461693B79B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/raw/Subproceso-Proceso-Area.xlsx
+++ b/data/raw/Subproceso-Proceso-Area.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="431" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D669B864-85E7-4E6B-AE1B-A9BCF0892C35}"/>
+  <xr:revisionPtr revIDLastSave="433" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8389ED76-DC05-4B09-8C55-CBC589E32477}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C8BB491-4D7A-4ED1-AB08-0ADDFA03A5A0}"/>
+    <workbookView xWindow="3696" yWindow="744" windowWidth="17280" windowHeight="8880" xr2:uid="{7C8BB491-4D7A-4ED1-AB08-0ADDFA03A5A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Proceso" sheetId="9" r:id="rId1"/>
@@ -31,7 +31,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId9"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1602,7 +1602,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{692C4F03-8B8F-4909-A847-49A10CEFB19B}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B44" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -2940,7 +2940,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D53" xr:uid="{556B4589-4764-4BC7-BA72-702E47300540}"/>
   <conditionalFormatting sqref="B3">
     <cfRule type="duplicateValues" dxfId="7" priority="1"/>
   </conditionalFormatting>
@@ -8497,6 +8496,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
@@ -8505,15 +8513,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8536,6 +8535,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -8544,12 +8551,4 @@
     <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/Subproceso-Proceso-Area.xlsx
+++ b/data/raw/Subproceso-Proceso-Area.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="433" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8389ED76-DC05-4B09-8C55-CBC589E32477}"/>
+  <xr:revisionPtr revIDLastSave="442" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1123AD19-A07D-48F3-853B-78A107DAFFA3}"/>
   <bookViews>
-    <workbookView xWindow="3696" yWindow="744" windowWidth="17280" windowHeight="8880" xr2:uid="{7C8BB491-4D7A-4ED1-AB08-0ADDFA03A5A0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C8BB491-4D7A-4ED1-AB08-0ADDFA03A5A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Proceso" sheetId="9" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja1!$A$1:$G$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Hoja1 (2)'!$A$1:$H$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Hoja2!$A$1:$D$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proceso!$A$1:$D$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proceso!$A$1:$D$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Rectoria!$A$1:$F$60</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="220">
   <si>
     <t>Área</t>
   </si>
@@ -710,6 +710,9 @@
   </si>
   <si>
     <t>Vicerrectoría financiera y administrativa</t>
+  </si>
+  <si>
+    <t>Estudios Internos</t>
   </si>
 </sst>
 </file>
@@ -929,7 +932,17 @@
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1023,10 +1036,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2188,7 +2197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{556B4589-4764-4BC7-BA72-702E47300540}">
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.21875" bestFit="1" customWidth="1"/>
@@ -2939,12 +2948,30 @@
         <v>151</v>
       </c>
     </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:D54" xr:uid="{556B4589-4764-4BC7-BA72-702E47300540}"/>
   <conditionalFormatting sqref="B3">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C51">
-    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C54">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4252,10 +4279,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C55">
-    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5746,10 +5773,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B56">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6531,7 +6558,7 @@
     </filterColumn>
   </autoFilter>
   <conditionalFormatting sqref="B2:B52">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7607,7 +7634,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B53">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8261,6 +8288,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -8495,27 +8542,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12D41D8-D34A-4C1F-82E4-8461693B79B3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8532,23 +8578,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/Subproceso-Proceso-Area.xlsx
+++ b/data/raw/Subproceso-Proceso-Area.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/lxisilva_poligran_edu_co/Documents/Documentos/Proyectos/Sistema_Indicadores_Poli/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="442" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1123AD19-A07D-48F3-853B-78A107DAFFA3}"/>
@@ -2971,7 +2971,7 @@
     <cfRule type="duplicateValues" dxfId="7" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C54">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4279,10 +4279,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3">
-    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C55">
-    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5773,10 +5773,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B56">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6558,7 +6558,7 @@
     </filterColumn>
   </autoFilter>
   <conditionalFormatting sqref="B2:B52">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7634,7 +7634,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B53">
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8299,15 +8299,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -8542,6 +8533,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
   <ds:schemaRefs>
@@ -8554,14 +8554,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12D41D8-D34A-4C1F-82E4-8461693B79B3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8578,4 +8570,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/Subproceso-Proceso-Area.xlsx
+++ b/data/raw/Subproceso-Proceso-Area.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="442" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1123AD19-A07D-48F3-853B-78A107DAFFA3}"/>
+  <xr:revisionPtr revIDLastSave="448" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B684AAB-5DB0-455B-A483-9256EC26AA0F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C8BB491-4D7A-4ED1-AB08-0ADDFA03A5A0}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="221">
   <si>
     <t>Área</t>
   </si>
@@ -713,6 +713,9 @@
   </si>
   <si>
     <t>Estudios Internos</t>
+  </si>
+  <si>
+    <t>Operación de Nuevos Negocios y CI</t>
   </si>
 </sst>
 </file>
@@ -2799,10 +2802,10 @@
         <v>16</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>118</v>
+        <v>220</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>151</v>
@@ -8288,14 +8291,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8534,21 +8535,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8573,9 +8573,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/raw/Subproceso-Proceso-Area.xlsx
+++ b/data/raw/Subproceso-Proceso-Area.xlsx
@@ -1039,6 +1039,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8300,6 +8304,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -8534,17 +8549,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="787dcc16-ad9c-4aed-8595-d8b714944830">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
   <ds:schemaRefs>
@@ -8554,6 +8558,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
+    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12D41D8-D34A-4C1F-82E4-8461693B79B3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8570,15 +8585,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eb4e1f33-0654-4877-a695-74ac1243131b"/>
-    <ds:schemaRef ds:uri="787dcc16-ad9c-4aed-8595-d8b714944830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/raw/Subproceso-Proceso-Area.xlsx
+++ b/data/raw/Subproceso-Proceso-Area.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="448" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B684AAB-5DB0-455B-A483-9256EC26AA0F}"/>
+  <xr:revisionPtr revIDLastSave="506" documentId="13_ncr:1_{7D5D2E2B-8870-4A5C-A9AF-FD632C2BB311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D258C33-39AF-4F76-BDBE-D4D7BC124237}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C8BB491-4D7A-4ED1-AB08-0ADDFA03A5A0}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="222">
   <si>
     <t>Área</t>
   </si>
@@ -716,6 +716,9 @@
   </si>
   <si>
     <t>Operación de Nuevos Negocios y CI</t>
+  </si>
+  <si>
+    <t>Vicerrectoría de crecimiento</t>
   </si>
 </sst>
 </file>
@@ -1039,10 +1042,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2817,7 +2816,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>122</v>
+        <v>221</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>121</v>
@@ -2887,7 +2886,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>122</v>
+        <v>221</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>121</v>
@@ -2901,7 +2900,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>122</v>
+        <v>221</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>121</v>
@@ -8295,15 +8294,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="eb4e1f33-0654-4877-a695-74ac1243131b" xsi:nil="true"/>
@@ -8314,7 +8304,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0772d54a1d010170e6fbd4301e22082d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d309db89fd7fb813f1d992ce290f04b6" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -8549,15 +8539,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50A7858D-C4BB-4738-AFE6-ACA2D8E7AA74}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -8568,7 +8559,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12D41D8-D34A-4C1F-82E4-8461693B79B3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8585,4 +8576,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE277362-6D14-47AE-9D5E-D8EAD6BC850B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>